--- a/08_tables/q12_split_sample_twfe_summary.xlsx
+++ b/08_tables/q12_split_sample_twfe_summary.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,72 +417,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Dependent variable</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Start year</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>End year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Observations</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Coefficient i</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>P-value i</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Coefficient GDP</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>P-value GDP</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Coefficient UN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P-value UN</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Coefficient REER</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>P-value REER</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>R-squared</t>
         </is>
@@ -521,31 +509,31 @@
         <v>551</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.02467736385555916</v>
+        <v>-0.02467736385555921</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6502034982446894</v>
+        <v>0.897154686399114</v>
       </c>
       <c r="H2" t="n">
-        <v>7.51787616960559e-07</v>
+        <v>7.517876169605593e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.261977820021798e-07</v>
+        <v>0.0008549454252837485</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009216810182634968</v>
+        <v>0.0009216810182635811</v>
       </c>
       <c r="K2" t="n">
-        <v>0.985765248637152</v>
+        <v>0.9936975296440351</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.00722608795248515</v>
+        <v>-0.007226087952485157</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5391242675218324</v>
+        <v>0.7081079613099015</v>
       </c>
       <c r="N2" t="n">
-        <v>0.05676049518050263</v>
+        <v>0.05676049518050297</v>
       </c>
     </row>
     <row r="3">
@@ -569,31 +557,31 @@
         <v>180</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3657482345808827</v>
+        <v>-0.3657482345808831</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08526933946274196</v>
+        <v>0.2194491249788588</v>
       </c>
       <c r="H3" t="n">
-        <v>8.331740912863463e-07</v>
+        <v>8.331740912863469e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03648329010524676</v>
+        <v>0.05702431773289973</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.06827097472370765</v>
+        <v>-0.06827097472370769</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2967661115543525</v>
+        <v>0.3468603390431464</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.02330306235119542</v>
+        <v>-0.02330306235119544</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1941575452080222</v>
+        <v>0.522604733902611</v>
       </c>
       <c r="N3" t="n">
-        <v>0.04402826588232722</v>
+        <v>0.044028265882327</v>
       </c>
     </row>
     <row r="4">
@@ -617,31 +605,31 @@
         <v>551</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7179145044263786</v>
+        <v>-0.7179145044263784</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03075452895336084</v>
+        <v>0.1356329323760417</v>
       </c>
       <c r="H4" t="n">
-        <v>4.334958044240548e-06</v>
+        <v>4.33495804424055e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>5.502851929684027e-07</v>
+        <v>0.04231050123931213</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2677949861021617</v>
+        <v>0.2677949861021615</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3950787527574489</v>
+        <v>0.7753890986813725</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2972557036418627</v>
+        <v>-0.2972557036418628</v>
       </c>
       <c r="M4" t="n">
-        <v>3.930472803714835e-05</v>
+        <v>0.1142485169409388</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07516947627853154</v>
+        <v>0.07516947627853143</v>
       </c>
     </row>
     <row r="5">
@@ -665,31 +653,31 @@
         <v>180</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4254262455590708</v>
+        <v>-0.4254262455590709</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09899984528322525</v>
+        <v>0.1917670025991263</v>
       </c>
       <c r="H5" t="n">
-        <v>5.492913635058617e-07</v>
+        <v>5.492913635058614e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2535268301099631</v>
+        <v>0.3858696206952303</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.05793997540090006</v>
+        <v>-0.05793997540090009</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4652772810580357</v>
+        <v>0.5684112292145971</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.01081833095312712</v>
+        <v>-0.01081833095312713</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6186434348667094</v>
+        <v>0.566227946519301</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0219704998155108</v>
+        <v>0.02197049981551058</v>
       </c>
     </row>
   </sheetData>
